--- a/excel/xiaoqian.xlsx
+++ b/excel/xiaoqian.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="99">
   <si>
     <t>序号</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>中文台词</t>
+  </si>
+  <si>
+    <t>音频</t>
   </si>
   <si>
     <t>字幕编码</t>
@@ -979,7 +982,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1005,14 +1008,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1555,22 +1561,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15.2"/>
   <cols>
     <col min="1" max="1" width="5" style="3" customWidth="1"/>
     <col min="2" max="2" width="33.1785714285714" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.28571428571429" style="3" customWidth="1"/>
     <col min="4" max="4" width="48.7857142857143" style="3" customWidth="1"/>
-    <col min="5" max="5" width="36.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="59.8214285714286" style="3" customWidth="1"/>
-    <col min="7" max="7" width="55.5089285714286" style="3" customWidth="1"/>
-    <col min="8" max="8" width="37.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.4285714285714" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9.14285714285714" style="3"/>
+    <col min="5" max="6" width="36.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="59.8214285714286" style="3" customWidth="1"/>
+    <col min="8" max="8" width="55.5089285714286" style="3" customWidth="1"/>
+    <col min="9" max="9" width="37.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.4285714285714" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9.14285714285714" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1589,486 +1595,512 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-    </row>
-    <row r="2" ht="17" spans="1:9">
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+    </row>
+    <row r="2" ht="17" spans="1:10">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-    </row>
-    <row r="3" ht="17" spans="1:9">
+      <c r="F2" s="10"/>
+      <c r="G2" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+    </row>
+    <row r="3" ht="17" spans="1:10">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-    </row>
-    <row r="4" ht="17" spans="1:9">
+      <c r="F3" s="10"/>
+      <c r="G3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+    </row>
+    <row r="4" ht="17" spans="1:10">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" ht="17" spans="1:9">
+      <c r="F4" s="10"/>
+      <c r="G4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+    </row>
+    <row r="5" ht="17" spans="1:10">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" ht="17" spans="1:9">
+      <c r="F5" s="10"/>
+      <c r="G5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" ht="17" spans="1:10">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" ht="17" spans="1:9">
+      <c r="F6" s="10"/>
+      <c r="G6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" ht="17" spans="1:10">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" ht="17" spans="1:6">
+      <c r="F7" s="10"/>
+      <c r="G7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" ht="17" spans="1:7">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" ht="17" spans="1:6">
+      <c r="F8" s="10"/>
+      <c r="G8" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:7">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" ht="17" spans="1:6">
+      <c r="F9" s="10"/>
+      <c r="G9" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="1:7">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" ht="17" spans="1:6">
+      <c r="F10" s="10"/>
+      <c r="G10" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:7">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" ht="17" spans="1:6">
+      <c r="F11" s="10"/>
+      <c r="G11" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="17" spans="1:7">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" ht="17" spans="1:6">
+      <c r="F12" s="10"/>
+      <c r="G12" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" ht="17" spans="1:7">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" ht="17" spans="1:6">
+      <c r="F13" s="10"/>
+      <c r="G13" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" ht="17" spans="1:7">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="15" ht="17" spans="1:6">
+      <c r="F14" s="10"/>
+      <c r="G14" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" ht="17" spans="1:7">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="16" ht="17" spans="1:6">
+      <c r="F15" s="10"/>
+      <c r="G15" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="17" spans="1:7">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" ht="17" spans="1:6">
+      <c r="E16" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" ht="17" spans="1:7">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18" ht="17" spans="1:6">
+      <c r="F17" s="10"/>
+      <c r="G17" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" ht="17" spans="1:7">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="E18" s="9" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="19" ht="17" spans="1:6">
+      <c r="F18" s="10"/>
+      <c r="G18" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" ht="17" spans="1:7">
       <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="E19" s="9" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="20" ht="17" spans="1:6">
+      <c r="F19" s="10"/>
+      <c r="G19" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" ht="17" spans="1:7">
       <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="E20" s="9" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" ht="17" spans="1:6">
+      <c r="F20" s="10"/>
+      <c r="G20" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" ht="17" spans="1:7">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="E21" s="9" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="22" ht="17" spans="1:6">
+      <c r="F21" s="10"/>
+      <c r="G21" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" ht="17" spans="1:7">
       <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" ht="17" spans="1:6">
+      <c r="E22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" ht="17" spans="1:7">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" ht="17" spans="1:6">
+      <c r="E23" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" ht="17" spans="1:7">
       <c r="A24" s="5">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="9" t="s">
         <v>97</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2090,117 +2122,117 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:1">

--- a/excel/xiaoqian.xlsx
+++ b/excel/xiaoqian.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
   <si>
     <t>序号</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>中文台词</t>
-  </si>
-  <si>
-    <t>音频</t>
   </si>
   <si>
     <t>字幕编码</t>
@@ -346,7 +343,6 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="0"/>
       <scheme val="major"/>
     </font>
@@ -363,7 +359,6 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
@@ -982,7 +977,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1011,14 +1006,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1561,22 +1550,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15.2"/>
   <cols>
     <col min="1" max="1" width="5" style="3" customWidth="1"/>
     <col min="2" max="2" width="33.1785714285714" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.28571428571429" style="3" customWidth="1"/>
     <col min="4" max="4" width="48.7857142857143" style="3" customWidth="1"/>
-    <col min="5" max="6" width="36.5" style="3" customWidth="1"/>
-    <col min="7" max="7" width="59.8214285714286" style="3" customWidth="1"/>
-    <col min="8" max="8" width="55.5089285714286" style="3" customWidth="1"/>
-    <col min="9" max="9" width="37.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.4285714285714" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.14285714285714" style="3"/>
+    <col min="5" max="5" width="36.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="59.8214285714286" style="3" customWidth="1"/>
+    <col min="7" max="7" width="55.5089285714286" style="3" customWidth="1"/>
+    <col min="8" max="8" width="37.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.4285714285714" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="9.14285714285714" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1595,512 +1584,479 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" ht="17" spans="1:10">
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" ht="17" spans="1:9">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" ht="17" spans="1:10">
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" ht="17" spans="1:9">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" ht="17" spans="1:10">
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+    </row>
+    <row r="4" ht="17" spans="1:9">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-    </row>
-    <row r="5" ht="17" spans="1:10">
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" ht="17" spans="1:9">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-    </row>
-    <row r="6" ht="17" spans="1:10">
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" ht="17" spans="1:9">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-    </row>
-    <row r="7" ht="17" spans="1:10">
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" ht="17" spans="1:9">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" ht="17" spans="1:7">
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" ht="17" spans="1:6">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" ht="17" spans="1:7">
+    </row>
+    <row r="9" ht="17" spans="1:6">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" ht="17" spans="1:7">
+    </row>
+    <row r="10" ht="17" spans="1:6">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" ht="17" spans="1:7">
+    </row>
+    <row r="11" ht="17" spans="1:6">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" ht="17" spans="1:7">
+    </row>
+    <row r="12" ht="17" spans="1:6">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" ht="17" spans="1:7">
+    </row>
+    <row r="13" ht="17" spans="1:6">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14" ht="17" spans="1:7">
+    </row>
+    <row r="14" ht="17" spans="1:6">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" ht="17" spans="1:7">
+    </row>
+    <row r="15" ht="17" spans="1:6">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" ht="17" spans="1:7">
+    </row>
+    <row r="16" ht="17" spans="1:6">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" ht="17" spans="1:7">
+      <c r="F16" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" ht="17" spans="1:6">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" ht="17" spans="1:7">
+    </row>
+    <row r="18" ht="17" spans="1:6">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="F18" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" ht="17" spans="1:7">
+    </row>
+    <row r="19" ht="17" spans="1:6">
       <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" ht="17" spans="1:7">
+    </row>
+    <row r="20" ht="17" spans="1:6">
       <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="F20" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" ht="17" spans="1:7">
+    </row>
+    <row r="21" ht="17" spans="1:6">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" ht="17" spans="1:7">
+    </row>
+    <row r="22" ht="17" spans="1:6">
       <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" ht="17" spans="1:7">
+      <c r="F22" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" ht="17" spans="1:6">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" ht="17" spans="1:7">
+      <c r="F23" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" ht="17" spans="1:6">
       <c r="A24" s="5">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="F24" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="11" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2122,117 +2078,117 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:1">
